--- a/main/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="204">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -426,6 +426,9 @@
   </si>
   <si>
     <t>Statut</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>Valeur issue du jdv-hl7-condition-clinical-cisis (2.16.840.1.113883.4.642.3.164)</t>
@@ -599,7 +602,7 @@
     <t>Sévérité de la manifestion</t>
   </si>
   <si>
-    <t>(preferred): SNOMED_CT =&gt; Valeur issue du jdv-severite-observation-cisis (1.2.250.1.213.1.1.5.675)</t>
+    <t>SNOMED_CT =&gt; Valeur issue du jdv-severite-observation-cisis (1.2.250.1.213.1.1.5.675)</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-severite-observation-cisis|20260619134042</t>
@@ -978,7 +981,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="80.41015625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="70.765625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="72.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2662,13 +2665,13 @@
         <v>73</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2686,7 +2689,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2703,10 +2706,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2732,10 +2735,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2786,7 +2789,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2803,10 +2806,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2832,10 +2835,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2886,7 +2889,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2903,10 +2906,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2932,10 +2935,10 @@
         <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2962,13 +2965,13 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2986,7 +2989,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3003,10 +3006,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3032,10 +3035,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3086,7 +3089,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3103,10 +3106,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3129,13 +3132,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3186,7 +3189,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3198,15 +3201,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3229,13 +3232,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3286,7 +3289,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3303,14 +3306,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3329,16 +3332,16 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3376,19 +3379,19 @@
         <v>73</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3400,15 +3403,15 @@
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3431,16 +3434,16 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3490,7 +3493,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3507,10 +3510,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3533,13 +3536,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3590,7 +3593,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3602,15 +3605,15 @@
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3636,10 +3639,10 @@
         <v>127</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3690,7 +3693,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3707,10 +3710,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3736,10 +3739,10 @@
         <v>127</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3790,7 +3793,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3807,10 +3810,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3836,10 +3839,10 @@
         <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3866,13 +3869,13 @@
         <v>73</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -3890,7 +3893,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3907,10 +3910,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3936,10 +3939,10 @@
         <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3990,7 +3993,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4007,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4033,13 +4036,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4090,7 +4093,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4107,10 +4110,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4136,10 +4139,10 @@
         <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4190,7 +4193,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4207,10 +4210,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4236,10 +4239,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4266,13 +4269,13 @@
         <v>73</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>73</v>
@@ -4290,7 +4293,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4307,10 +4310,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4333,13 +4336,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4390,7 +4393,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -4407,10 +4410,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4433,13 +4436,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4490,7 +4493,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
